--- a/filer/40333371_hellofresh.xlsx
+++ b/filer/40333371_hellofresh.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/40333371_hellofresh.xlsx
+++ b/filer/40333371_hellofresh.xlsx
@@ -202,8 +202,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +662,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +677,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1531,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2043,49 +2043,49 @@
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B33" s="11">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B33" s="8">
         <f>'balance_raw_40333371'!$B$12</f>
         <v/>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="8">
         <f>'balance_raw_40333371'!$C$12</f>
         <v/>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="8">
         <f>'balance_raw_40333371'!$D$12</f>
         <v/>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="8">
         <f>'balance_raw_40333371'!$E$12</f>
         <v/>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="8">
         <f>'balance_raw_40333371'!$F$12</f>
         <v/>
       </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" s="12">
+      <c r="H33" s="9">
         <f>IFERROR(B33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="9">
         <f>IFERROR(C33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="9">
         <f>IFERROR(D33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="9">
         <f>IFERROR(E33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="9">
         <f>IFERROR(F33/$B$33*100,"")</f>
         <v/>
       </c>
@@ -2093,7 +2093,7 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B34" s="5">
@@ -2141,7 +2141,7 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+          <t>Andre tilgodehavender</t>
         </is>
       </c>
       <c r="B35" s="8">
@@ -2189,7 +2189,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Andre tilgodehavender</t>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
       <c r="B36" s="5">
@@ -2237,7 +2237,7 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
+          <t>Udskudt skatteaktiv</t>
         </is>
       </c>
       <c r="B37" s="8">
@@ -2285,7 +2285,7 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Udskudt skatteaktiv</t>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B38" s="5">
@@ -2333,7 +2333,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+          <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
       <c r="B39" s="8">
@@ -2379,97 +2379,97 @@
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Kortfristede skattetilgodehavender</t>
-        </is>
-      </c>
-      <c r="B40" s="5">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B40" s="11">
         <f>'balance_raw_40333371'!$B$19</f>
         <v/>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="11">
         <f>'balance_raw_40333371'!$C$19</f>
         <v/>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="11">
         <f>'balance_raw_40333371'!$D$19</f>
         <v/>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="11">
         <f>'balance_raw_40333371'!$E$19</f>
         <v/>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="11">
         <f>'balance_raw_40333371'!$F$19</f>
         <v/>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" s="6">
+      <c r="H40" s="12">
         <f>IFERROR(B40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="12">
         <f>IFERROR(C40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="12">
         <f>IFERROR(D40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="12">
         <f>IFERROR(E40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="12">
         <f>IFERROR(F40/$B$40*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B41" s="11">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B41" s="8">
         <f>'balance_raw_40333371'!$B$20</f>
         <v/>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="8">
         <f>'balance_raw_40333371'!$C$20</f>
         <v/>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="8">
         <f>'balance_raw_40333371'!$D$20</f>
         <v/>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="8">
         <f>'balance_raw_40333371'!$E$20</f>
         <v/>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="8">
         <f>'balance_raw_40333371'!$F$20</f>
         <v/>
       </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" s="12">
+      <c r="H41" s="9">
         <f>IFERROR(B41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="I41" s="12">
+      <c r="I41" s="9">
         <f>IFERROR(C41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="J41" s="12">
+      <c r="J41" s="9">
         <f>IFERROR(D41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="K41" s="12">
+      <c r="K41" s="9">
         <f>IFERROR(E41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="L41" s="12">
+      <c r="L41" s="9">
         <f>IFERROR(F41/$B$41*100,"")</f>
         <v/>
       </c>
@@ -2477,7 +2477,7 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Værdipapirer</t>
+          <t>Likvide beholdninger</t>
         </is>
       </c>
       <c r="B42" s="5">
@@ -2523,49 +2523,49 @@
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>Likvide beholdninger</t>
-        </is>
-      </c>
-      <c r="B43" s="8">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B43" s="11">
         <f>'balance_raw_40333371'!$B$22</f>
         <v/>
       </c>
-      <c r="C43" s="8">
+      <c r="C43" s="11">
         <f>'balance_raw_40333371'!$C$22</f>
         <v/>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="11">
         <f>'balance_raw_40333371'!$D$22</f>
         <v/>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="11">
         <f>'balance_raw_40333371'!$E$22</f>
         <v/>
       </c>
-      <c r="F43" s="8">
+      <c r="F43" s="11">
         <f>'balance_raw_40333371'!$F$22</f>
         <v/>
       </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" s="9">
+      <c r="H43" s="12">
         <f>IFERROR(B43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="12">
         <f>IFERROR(C43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="J43" s="9">
+      <c r="J43" s="12">
         <f>IFERROR(D43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="K43" s="9">
+      <c r="K43" s="12">
         <f>IFERROR(E43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="L43" s="9">
+      <c r="L43" s="12">
         <f>IFERROR(F43/$B$43*100,"")</f>
         <v/>
       </c>
@@ -2573,7 +2573,7 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Omsætningsaktiver</t>
+          <t>Aktiver</t>
         </is>
       </c>
       <c r="B44" s="11">
@@ -2618,96 +2618,96 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B45" s="11">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>PASSIVER t.kr.</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B47" s="8">
         <f>'balance_raw_40333371'!$B$24</f>
         <v/>
       </c>
-      <c r="C45" s="11">
+      <c r="C47" s="8">
         <f>'balance_raw_40333371'!$C$24</f>
         <v/>
       </c>
-      <c r="D45" s="11">
+      <c r="D47" s="8">
         <f>'balance_raw_40333371'!$D$24</f>
         <v/>
       </c>
-      <c r="E45" s="11">
+      <c r="E47" s="8">
         <f>'balance_raw_40333371'!$E$24</f>
         <v/>
       </c>
-      <c r="F45" s="11">
+      <c r="F47" s="8">
         <f>'balance_raw_40333371'!$F$24</f>
         <v/>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" s="12">
-        <f>IFERROR(B45/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="12">
-        <f>IFERROR(C45/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="J45" s="12">
-        <f>IFERROR(D45/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="K45" s="12">
-        <f>IFERROR(E45/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="L45" s="12">
-        <f>IFERROR(F45/$B$45*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>PASSIVER t.kr.</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>2024</v>
-      </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J47" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="K47" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>2024</v>
+      <c r="H47" s="9">
+        <f>IFERROR(B47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="9">
+        <f>IFERROR(C47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="9">
+        <f>IFERROR(D47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="K47" s="9">
+        <f>IFERROR(E47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="9">
+        <f>IFERROR(F47/$B$47*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Selskabskapital</t>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
       <c r="B48" s="5">
@@ -2755,7 +2755,7 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+          <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
       <c r="B49" s="8">
@@ -2803,7 +2803,7 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Reserve for udviklingsomkostninger</t>
+          <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
       <c r="B50" s="5">
@@ -2851,7 +2851,7 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
+          <t>Andre reserver</t>
         </is>
       </c>
       <c r="B51" s="8">
@@ -2899,7 +2899,7 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Andre reserver</t>
+          <t>Overført resultat</t>
         </is>
       </c>
       <c r="B52" s="5">
@@ -2945,97 +2945,97 @@
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>Overført resultat</t>
-        </is>
-      </c>
-      <c r="B53" s="8">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B53" s="11">
         <f>'balance_raw_40333371'!$B$30</f>
         <v/>
       </c>
-      <c r="C53" s="8">
+      <c r="C53" s="11">
         <f>'balance_raw_40333371'!$C$30</f>
         <v/>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="11">
         <f>'balance_raw_40333371'!$D$30</f>
         <v/>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="11">
         <f>'balance_raw_40333371'!$E$30</f>
         <v/>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="11">
         <f>'balance_raw_40333371'!$F$30</f>
         <v/>
       </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" s="9">
+      <c r="H53" s="12">
         <f>IFERROR(B53/$B$53*100,"")</f>
         <v/>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="12">
         <f>IFERROR(C53/$B$53*100,"")</f>
         <v/>
       </c>
-      <c r="J53" s="9">
+      <c r="J53" s="12">
         <f>IFERROR(D53/$B$53*100,"")</f>
         <v/>
       </c>
-      <c r="K53" s="9">
+      <c r="K53" s="12">
         <f>IFERROR(E53/$B$53*100,"")</f>
         <v/>
       </c>
-      <c r="L53" s="9">
+      <c r="L53" s="12">
         <f>IFERROR(F53/$B$53*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B54" s="11">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B54" s="5">
         <f>'balance_raw_40333371'!$B$31</f>
         <v/>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="5">
         <f>'balance_raw_40333371'!$C$31</f>
         <v/>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="5">
         <f>'balance_raw_40333371'!$D$31</f>
         <v/>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="5">
         <f>'balance_raw_40333371'!$E$31</f>
         <v/>
       </c>
-      <c r="F54" s="11">
+      <c r="F54" s="5">
         <f>'balance_raw_40333371'!$F$31</f>
         <v/>
       </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" s="12">
+      <c r="H54" s="6">
         <f>IFERROR(B54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="I54" s="12">
+      <c r="I54" s="6">
         <f>IFERROR(C54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="J54" s="12">
+      <c r="J54" s="6">
         <f>IFERROR(D54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="K54" s="12">
+      <c r="K54" s="6">
         <f>IFERROR(E54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="L54" s="12">
+      <c r="L54" s="6">
         <f>IFERROR(F54/$B$54*100,"")</f>
         <v/>
       </c>
@@ -3043,7 +3043,7 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
+          <t>Langfristede lån</t>
         </is>
       </c>
       <c r="B55" s="8">
@@ -3091,7 +3091,7 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Langfristede lån</t>
+          <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
       <c r="B56" s="5">
@@ -3139,7 +3139,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (langfristet)</t>
+          <t>Anden gæld (langfristet)</t>
         </is>
       </c>
       <c r="B57" s="8">
@@ -3185,97 +3185,97 @@
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Anden gæld (langfristet)</t>
-        </is>
-      </c>
-      <c r="B58" s="5">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B58" s="11">
         <f>'balance_raw_40333371'!$B$35</f>
         <v/>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="11">
         <f>'balance_raw_40333371'!$C$35</f>
         <v/>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="11">
         <f>'balance_raw_40333371'!$D$35</f>
         <v/>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="11">
         <f>'balance_raw_40333371'!$E$35</f>
         <v/>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="11">
         <f>'balance_raw_40333371'!$F$35</f>
         <v/>
       </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" s="6">
+      <c r="H58" s="12">
         <f>IFERROR(B58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="I58" s="6">
+      <c r="I58" s="12">
         <f>IFERROR(C58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="J58" s="6">
+      <c r="J58" s="12">
         <f>IFERROR(D58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="K58" s="6">
+      <c r="K58" s="12">
         <f>IFERROR(E58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="L58" s="6">
+      <c r="L58" s="12">
         <f>IFERROR(F58/$B$58*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B59" s="11">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B59" s="8">
         <f>'balance_raw_40333371'!$B$36</f>
         <v/>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="8">
         <f>'balance_raw_40333371'!$C$36</f>
         <v/>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="8">
         <f>'balance_raw_40333371'!$D$36</f>
         <v/>
       </c>
-      <c r="E59" s="11">
+      <c r="E59" s="8">
         <f>'balance_raw_40333371'!$E$36</f>
         <v/>
       </c>
-      <c r="F59" s="11">
+      <c r="F59" s="8">
         <f>'balance_raw_40333371'!$F$36</f>
         <v/>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" s="12">
+      <c r="H59" s="9">
         <f>IFERROR(B59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="I59" s="12">
+      <c r="I59" s="9">
         <f>IFERROR(C59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="J59" s="12">
+      <c r="J59" s="9">
         <f>IFERROR(D59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="K59" s="12">
+      <c r="K59" s="9">
         <f>IFERROR(E59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="L59" s="12">
+      <c r="L59" s="9">
         <f>IFERROR(F59/$B$59*100,"")</f>
         <v/>
       </c>
@@ -3283,7 +3283,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B60" s="5">
@@ -3331,7 +3331,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B61" s="8">
@@ -3379,7 +3379,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B62" s="5">
@@ -3427,7 +3427,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B63" s="8">
@@ -3475,7 +3475,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B64" s="5">
@@ -3523,7 +3523,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B65" s="8">
@@ -3571,7 +3571,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B66" s="5">
@@ -3619,7 +3619,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
       <c r="B67" s="8">
@@ -3667,7 +3667,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+          <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
       <c r="B68" s="5">
@@ -3715,7 +3715,7 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
       <c r="B69" s="8">
@@ -3761,49 +3761,49 @@
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B70" s="5">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B70" s="11">
         <f>'balance_raw_40333371'!$B$47</f>
         <v/>
       </c>
-      <c r="C70" s="5">
+      <c r="C70" s="11">
         <f>'balance_raw_40333371'!$C$47</f>
         <v/>
       </c>
-      <c r="D70" s="5">
+      <c r="D70" s="11">
         <f>'balance_raw_40333371'!$D$47</f>
         <v/>
       </c>
-      <c r="E70" s="5">
+      <c r="E70" s="11">
         <f>'balance_raw_40333371'!$E$47</f>
         <v/>
       </c>
-      <c r="F70" s="5">
+      <c r="F70" s="11">
         <f>'balance_raw_40333371'!$F$47</f>
         <v/>
       </c>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" s="6">
+      <c r="H70" s="12">
         <f>IFERROR(B70/$B$70*100,"")</f>
         <v/>
       </c>
-      <c r="I70" s="6">
+      <c r="I70" s="12">
         <f>IFERROR(C70/$B$70*100,"")</f>
         <v/>
       </c>
-      <c r="J70" s="6">
+      <c r="J70" s="12">
         <f>IFERROR(D70/$B$70*100,"")</f>
         <v/>
       </c>
-      <c r="K70" s="6">
+      <c r="K70" s="12">
         <f>IFERROR(E70/$B$70*100,"")</f>
         <v/>
       </c>
-      <c r="L70" s="6">
+      <c r="L70" s="12">
         <f>IFERROR(F70/$B$70*100,"")</f>
         <v/>
       </c>
@@ -3811,7 +3811,7 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>Kortfristede gældsforpligtelser</t>
+          <t>Gældsforpligtelser</t>
         </is>
       </c>
       <c r="B71" s="11">
@@ -3859,7 +3859,7 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>Gældsforpligtelser</t>
+          <t>Passiver</t>
         </is>
       </c>
       <c r="B72" s="11">
@@ -3904,100 +3904,100 @@
         <v/>
       </c>
     </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B73" s="11">
-        <f>'balance_raw_40333371'!$B$50</f>
-        <v/>
-      </c>
-      <c r="C73" s="11">
-        <f>'balance_raw_40333371'!$C$50</f>
-        <v/>
-      </c>
-      <c r="D73" s="11">
-        <f>'balance_raw_40333371'!$D$50</f>
-        <v/>
-      </c>
-      <c r="E73" s="11">
-        <f>'balance_raw_40333371'!$E$50</f>
-        <v/>
-      </c>
-      <c r="F73" s="11">
-        <f>'balance_raw_40333371'!$F$50</f>
-        <v/>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" s="12">
-        <f>IFERROR(B73/$B$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="I73" s="12">
-        <f>IFERROR(C73/$B$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="J73" s="12">
-        <f>IFERROR(D73/$B$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="K73" s="12">
-        <f>IFERROR(E73/$B$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="L73" s="12">
-        <f>IFERROR(F73/$B$73*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>NØGLEOPLYSNINGER</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C75" s="3" t="n">
+      <c r="B74" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="C74" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="D74" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F75" s="3" t="n">
+      <c r="E74" s="3" t="n">
         <v>2024</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B75" s="8">
+        <f>'res_raw_40333371'!$B$19</f>
+        <v/>
+      </c>
+      <c r="C75" s="8">
+        <f>'res_raw_40333371'!$C$19</f>
+        <v/>
+      </c>
+      <c r="D75" s="8">
+        <f>'res_raw_40333371'!$D$19</f>
+        <v/>
+      </c>
+      <c r="E75" s="8">
+        <f>'res_raw_40333371'!$E$19</f>
+        <v/>
+      </c>
+      <c r="F75" s="8">
+        <f>'res_raw_40333371'!$F$19</f>
+        <v/>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" s="9">
+        <f>IFERROR(B75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="I75" s="9">
+        <f>IFERROR(C75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="J75" s="9">
+        <f>IFERROR(D75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="K75" s="9">
+        <f>IFERROR(E75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="L75" s="9">
+        <f>IFERROR(F75/$B$75*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Gns. antal medarbejdere</t>
+          <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
       <c r="B76" s="5">
-        <f>'res_raw_40333371'!$B$19</f>
+        <f>'res_raw_40333371'!$B$20</f>
         <v/>
       </c>
       <c r="C76" s="5">
-        <f>'res_raw_40333371'!$C$19</f>
+        <f>'res_raw_40333371'!$C$20</f>
         <v/>
       </c>
       <c r="D76" s="5">
-        <f>'res_raw_40333371'!$D$19</f>
+        <f>'res_raw_40333371'!$D$20</f>
         <v/>
       </c>
       <c r="E76" s="5">
-        <f>'res_raw_40333371'!$E$19</f>
+        <f>'res_raw_40333371'!$E$20</f>
         <v/>
       </c>
       <c r="F76" s="5">
-        <f>'res_raw_40333371'!$F$19</f>
+        <f>'res_raw_40333371'!$F$20</f>
         <v/>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -4022,371 +4022,330 @@
         <v/>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B77" s="8">
-        <f>'res_raw_40333371'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C77" s="8">
-        <f>'res_raw_40333371'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D77" s="8">
-        <f>'res_raw_40333371'!$D$20</f>
-        <v/>
-      </c>
-      <c r="E77" s="8">
-        <f>'res_raw_40333371'!$E$20</f>
-        <v/>
-      </c>
-      <c r="F77" s="8">
-        <f>'res_raw_40333371'!$F$20</f>
-        <v/>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" s="9">
-        <f>IFERROR(B77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="I77" s="9">
-        <f>IFERROR(C77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="J77" s="9">
-        <f>IFERROR(D77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="K77" s="9">
-        <f>IFERROR(E77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="L77" s="9">
-        <f>IFERROR(F77/$B$77*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>NØGLETAL</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C79" s="3" t="n">
+      <c r="B78" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="C78" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="D78" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="E78" s="3" t="n">
         <v>2024</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B79" s="13">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="C79" s="13">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="D79" s="13">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="E79" s="13">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="F79" s="13">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$44*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B80" s="13">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="C80" s="13">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="D80" s="13">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="E80" s="13">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="F80" s="13">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$45*100,"")</f>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B80" s="14">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="14">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="14">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E80" s="14">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F80" s="14">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B81" s="14">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="C81" s="14">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="D81" s="14">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="E81" s="14">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="F81" s="14">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B81" s="13">
+        <f>IFERROR($B$4/$B$44,"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="13">
+        <f>IFERROR($C$4/$C$44,"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="13">
+        <f>IFERROR($D$4/$D$44,"")</f>
+        <v/>
+      </c>
+      <c r="E81" s="13">
+        <f>IFERROR($E$4/$E$44,"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="13">
+        <f>IFERROR($F$4/$F$44,"")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B82" s="13">
-        <f>IFERROR($B$4/$B$45,"")</f>
-        <v/>
-      </c>
-      <c r="C82" s="13">
-        <f>IFERROR($C$4/$C$45,"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="13">
-        <f>IFERROR($D$4/$D$45,"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="13">
-        <f>IFERROR($E$4/$E$45,"")</f>
-        <v/>
-      </c>
-      <c r="F82" s="13">
-        <f>IFERROR($F$4/$F$45,"")</f>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B82" s="14">
+        <f>IFERROR($B$18/$B$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="14">
+        <f>IFERROR($C$18/$C$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="14">
+        <f>IFERROR($D$18/$D$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="14">
+        <f>IFERROR($E$18/$E$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="14">
+        <f>IFERROR($F$18/$F$53*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B83" s="14">
-        <f>IFERROR($B$18/$B$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="C83" s="14">
-        <f>IFERROR($C$18/$C$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="14">
-        <f>IFERROR($D$18/$D$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="14">
-        <f>IFERROR($E$18/$E$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="F83" s="14">
-        <f>IFERROR($F$18/$F$54*100,"")</f>
+          <t>Gældsrente, %</t>
+        </is>
+      </c>
+      <c r="B83" s="13">
+        <f>IFERROR($B$16/($B$72-$B$53)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="13">
+        <f>IFERROR($C$16/($C$72-$C$53)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="13">
+        <f>IFERROR($D$16/($D$72-$D$53)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="13">
+        <f>IFERROR($E$16/($E$72-$E$53)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="13">
+        <f>IFERROR($F$16/($F$72-$F$53)*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
-        </is>
-      </c>
-      <c r="B84" s="13">
-        <f>IFERROR($B$16/($B$73-$B$54)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C84" s="13">
-        <f>IFERROR($C$16/($C$73-$C$54)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D84" s="13">
-        <f>IFERROR($D$16/($D$73-$D$54)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E84" s="13">
-        <f>IFERROR($E$16/($E$73-$E$54)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F84" s="13">
-        <f>IFERROR($F$16/($F$73-$F$54)*100,"")</f>
+          <t>Soliditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B84" s="14">
+        <f>IFERROR($B$53/$B$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="14">
+        <f>IFERROR($C$53/$C$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="14">
+        <f>IFERROR($D$53/$D$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="14">
+        <f>IFERROR($E$53/$E$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="14">
+        <f>IFERROR($F$53/$F$44*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B85" s="14">
-        <f>IFERROR($B$54/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="C85" s="14">
-        <f>IFERROR($C$54/$C$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="D85" s="14">
-        <f>IFERROR($D$54/$D$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="E85" s="14">
-        <f>IFERROR($E$54/$E$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="F85" s="14">
-        <f>IFERROR($F$54/$F$45*100,"")</f>
+          <t>Gearing</t>
+        </is>
+      </c>
+      <c r="B85" s="13">
+        <f>IFERROR(($B$72-$B$53)/$B$53,"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="13">
+        <f>IFERROR(($C$72-$C$53)/$C$53,"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="13">
+        <f>IFERROR(($D$72-$D$53)/$D$53,"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="13">
+        <f>IFERROR(($E$72-$E$53)/$E$53,"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="13">
+        <f>IFERROR(($F$72-$F$53)/$F$53,"")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Gearing</t>
-        </is>
-      </c>
-      <c r="B86" s="13">
-        <f>IFERROR(($B$73-$B$54)/$B$54,"")</f>
-        <v/>
-      </c>
-      <c r="C86" s="13">
-        <f>IFERROR(($C$73-$C$54)/$C$54,"")</f>
-        <v/>
-      </c>
-      <c r="D86" s="13">
-        <f>IFERROR(($D$73-$D$54)/$D$54,"")</f>
-        <v/>
-      </c>
-      <c r="E86" s="13">
-        <f>IFERROR(($E$73-$E$54)/$E$54,"")</f>
-        <v/>
-      </c>
-      <c r="F86" s="13">
-        <f>IFERROR(($F$73-$F$54)/$F$54,"")</f>
+          <t>Likviditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B86" s="14">
+        <f>IFERROR($B$43/$B$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="14">
+        <f>IFERROR($C$43/$C$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="14">
+        <f>IFERROR($D$43/$D$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="14">
+        <f>IFERROR($E$43/$E$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="14">
+        <f>IFERROR($F$43/$F$70*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B87" s="14">
-        <f>IFERROR($B$44/$B$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="C87" s="14">
-        <f>IFERROR($C$44/$C$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="D87" s="14">
-        <f>IFERROR($D$44/$D$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="E87" s="14">
-        <f>IFERROR($E$44/$E$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="F87" s="14">
-        <f>IFERROR($F$44/$F$71*100,"")</f>
+          <t>Rentemarginal, %</t>
+        </is>
+      </c>
+      <c r="B87" s="13">
+        <f>IFERROR(B79-B83,"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="13">
+        <f>IFERROR(C79-C83,"")</f>
+        <v/>
+      </c>
+      <c r="D87" s="13">
+        <f>IFERROR(D79-D83,"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="13">
+        <f>IFERROR(E79-E83,"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="13">
+        <f>IFERROR(F79-F83,"")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Rentemarginal, %</t>
-        </is>
-      </c>
-      <c r="B88" s="13">
-        <f>IFERROR(B80-B84,"")</f>
-        <v/>
-      </c>
-      <c r="C88" s="13">
-        <f>IFERROR(C80-C84,"")</f>
-        <v/>
-      </c>
-      <c r="D88" s="13">
-        <f>IFERROR(D80-D84,"")</f>
-        <v/>
-      </c>
-      <c r="E88" s="13">
-        <f>IFERROR(E80-E84,"")</f>
-        <v/>
-      </c>
-      <c r="F88" s="13">
-        <f>IFERROR(F80-F84,"")</f>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B88" s="14">
+        <f>IFERROR(($B$72-$B$53)/$B$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="C88" s="14">
+        <f>IFERROR(($C$72-$C$53)/$C$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="D88" s="14">
+        <f>IFERROR(($D$72-$D$53)/$D$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="E88" s="14">
+        <f>IFERROR(($E$72-$E$53)/$E$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="14">
+        <f>IFERROR(($F$72-$F$53)/$F$44*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B89" s="14">
-        <f>IFERROR(($B$73-$B$54)/$B$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="C89" s="14">
-        <f>IFERROR(($C$73-$C$54)/$C$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="D89" s="14">
-        <f>IFERROR(($D$73-$D$54)/$D$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="E89" s="14">
-        <f>IFERROR(($E$73-$E$54)/$E$45*100,"")</f>
-        <v/>
-      </c>
-      <c r="F89" s="14">
-        <f>IFERROR(($F$73-$F$54)/$F$45*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
           <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
-      <c r="B90" s="13">
-        <f>IFERROR($B$32/($B$54+$B$59)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C90" s="13">
-        <f>IFERROR($C$32/($C$54+$C$59)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D90" s="13">
-        <f>IFERROR($D$32/($D$54+$D$59)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E90" s="13">
-        <f>IFERROR($E$32/($E$54+$E$59)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F90" s="13">
-        <f>IFERROR($F$32/($F$54+$F$59)*100,"")</f>
-        <v/>
+      <c r="B89" s="13">
+        <f>IFERROR($B$32/($B$53+$B$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="13">
+        <f>IFERROR($C$32/($C$53+$C$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="13">
+        <f>IFERROR($D$32/($D$53+$D$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E89" s="13">
+        <f>IFERROR($E$32/($E$53+$E$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F89" s="13">
+        <f>IFERROR($F$32/($F$53+$F$58)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4418,19 +4377,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4440,19 +4399,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>74251</v>
+        <v>539751</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>539751</v>
+        <v>809082</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>809082</v>
+        <v>836929</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>836929</v>
+        <v>770270</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>770270</v>
+        <v>734185</v>
       </c>
     </row>
     <row r="3">
@@ -4473,18 +4432,20 @@
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
+      <c r="B4" s="16" t="n">
+        <v>423201</v>
+      </c>
       <c r="C4" s="16" t="n">
-        <v>423201</v>
+        <v>576365</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>576365</v>
+        <v>494763</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>494763</v>
+        <v>374538</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>374538</v>
+        <v>330536</v>
       </c>
     </row>
     <row r="5">
@@ -4493,18 +4454,20 @@
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
+      <c r="B5" s="16" t="n">
+        <v>87409</v>
+      </c>
       <c r="C5" s="16" t="n">
-        <v>87409</v>
+        <v>148869</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>148869</v>
+        <v>222024</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>222024</v>
+        <v>283834</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>283834</v>
+        <v>308858</v>
       </c>
     </row>
     <row r="6">
@@ -4514,19 +4477,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>2021</v>
+        <v>29140</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>29140</v>
+        <v>83848</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>83848</v>
+        <v>120142</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>120142</v>
+        <v>111898</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>111898</v>
+        <v>94791</v>
       </c>
     </row>
     <row r="7">
@@ -4536,19 +4499,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>13297</v>
+        <v>27765</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>27765</v>
+        <v>57996</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>57996</v>
+        <v>86555</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>86555</v>
+        <v>85024</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>85024</v>
+        <v>86575</v>
       </c>
     </row>
     <row r="8">
@@ -4565,19 +4528,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>193</v>
+        <v>624</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>624</v>
+        <v>821</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>821</v>
+        <v>964</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>964</v>
+        <v>690</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>690</v>
+        <v>460</v>
       </c>
     </row>
     <row r="10">
@@ -4599,19 +4562,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>-11469</v>
+        <v>752</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>752</v>
+        <v>25031</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>25031</v>
+        <v>32623</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>32623</v>
+        <v>26185</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>26185</v>
+        <v>7756</v>
       </c>
     </row>
     <row r="12">
@@ -4633,19 +4596,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>465</v>
+        <v>2735</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>2735</v>
+        <v>9287</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>9287</v>
+        <v>11096</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>11096</v>
+        <v>10586</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>10586</v>
+        <v>14652</v>
       </c>
     </row>
     <row r="14">
@@ -4655,19 +4618,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>1196</v>
+        <v>4888</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>4888</v>
+        <v>13875</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>13875</v>
+        <v>11973</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>11973</v>
+        <v>6945</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>6945</v>
+        <v>18197</v>
       </c>
     </row>
     <row r="15">
@@ -4676,19 +4639,19 @@
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
+      <c r="B15" s="16" t="n">
+        <v>-2153</v>
+      </c>
       <c r="C15" s="16" t="n">
-        <v>-2153</v>
+        <v>-4588</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>-4588</v>
+        <v>-876</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>-876</v>
-      </c>
-      <c r="F15" s="16" t="n">
         <v>3641</v>
       </c>
+      <c r="F15" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -4697,19 +4660,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>-12200</v>
+        <v>-1402</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>-1402</v>
+        <v>20443</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>20443</v>
+        <v>31746</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>31746</v>
+        <v>29826</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>29826</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="17">
@@ -4719,19 +4682,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>-2761</v>
+        <v>-280</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>-280</v>
+        <v>4635</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>4635</v>
+        <v>7105</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>7105</v>
+        <v>6616</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>6616</v>
+        <v>808</v>
       </c>
     </row>
     <row r="18">
@@ -4741,19 +4704,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>-9440</v>
+        <v>-1122</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>-1122</v>
+        <v>15808</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>15808</v>
+        <v>24642</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>24642</v>
+        <v>23209</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>23209</v>
+        <v>3403</v>
       </c>
     </row>
     <row r="19">
@@ -4763,19 +4726,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20">
@@ -4785,20 +4748,18 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>2285</v>
+        <v>1324</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>1324</v>
+        <v>342</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>342</v>
+        <v>628</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>628</v>
-      </c>
-      <c r="F20" s="16" t="n">
         <v>245</v>
       </c>
+      <c r="F20" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4811,7 +4772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4829,19 +4790,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4875,19 +4836,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>788</v>
+        <v>1692</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>1692</v>
+        <v>1305</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1305</v>
+        <v>731</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>731</v>
+        <v>787</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>787</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="5">
@@ -4897,19 +4858,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>920</v>
+        <v>716</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>716</v>
+        <v>625</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>625</v>
+        <v>383</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>383</v>
+        <v>105</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4920,13 +4881,13 @@
       </c>
       <c r="B6" s="16" t="n"/>
       <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
+      <c r="D6" s="16" t="n">
+        <v>223</v>
+      </c>
       <c r="E6" s="16" t="n">
-        <v>223</v>
-      </c>
-      <c r="F6" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="F6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
@@ -4935,19 +4896,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>1708</v>
+        <v>2408</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>2408</v>
+        <v>1930</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>1930</v>
+        <v>1336</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>1336</v>
+        <v>891</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>891</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="8">
@@ -4957,13 +4918,13 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>35</v>
+        <v>224318</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>224318</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>224318</v>
+        <v>293022</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>293022</v>
@@ -4979,19 +4940,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>454</v>
+        <v>658</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>658</v>
+        <v>602</v>
       </c>
       <c r="D9" s="16" t="n">
+        <v>631</v>
+      </c>
+      <c r="E9" s="16" t="n">
         <v>602</v>
       </c>
-      <c r="E9" s="16" t="n">
-        <v>631</v>
-      </c>
       <c r="F9" s="16" t="n">
-        <v>602</v>
+        <v>883</v>
       </c>
     </row>
     <row r="10">
@@ -5001,19 +4962,19 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>489</v>
+        <v>239866</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>239866</v>
+        <v>224920</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>224920</v>
+        <v>293653</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>293653</v>
+        <v>293625</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>293625</v>
+        <v>293905</v>
       </c>
     </row>
     <row r="11">
@@ -5023,299 +4984,295 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>2198</v>
+        <v>242274</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>242274</v>
+        <v>226850</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>226850</v>
+        <v>294990</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>294990</v>
+        <v>294516</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>294516</v>
+        <v>294989</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+        <v>99</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>431</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>822</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>776</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>14693</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>5600</v>
+        <v>2893</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>99</v>
+        <v>30652</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>431</v>
+        <v>5268</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>822</v>
+        <v>74498</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>776</v>
+        <v>85228</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+          <t>Andre tilgodehavender</t>
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>3795</v>
+        <v>1563</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>2893</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>30652</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>5268</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>74498</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Andre tilgodehavender</t>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>1563</v>
+        <v>290</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+        <v>375</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>392</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>970</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
+          <t>Udskudt skatteaktiv</t>
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>513</v>
+        <v>3049</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>290</v>
+        <v>165</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>375</v>
+        <v>131</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>392</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Udskudt skatteaktiv</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>2769</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>3049</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>137</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>165</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>131</v>
-      </c>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+          <t>Kortfristede skattetilgodehavender</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>3478</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>395</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>2312</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristede skattetilgodehavender</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>7780</v>
+      </c>
       <c r="C19" s="16" t="n">
-        <v>0</v>
+        <v>34988</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>3478</v>
+        <v>6629</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0</v>
+        <v>76191</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>395</v>
+        <v>103279</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>12677</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>7780</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>34988</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>6629</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>76191</v>
-      </c>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>111522</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>104229</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>65599</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>9110</v>
+      </c>
       <c r="F21" s="16" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Likvide beholdninger</t>
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>21459</v>
+        <v>119302</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>111522</v>
+        <v>139217</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>104229</v>
+        <v>72229</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>65599</v>
+        <v>85301</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>9110</v>
+        <v>103279</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>Omsætningsaktiver</t>
+          <t>Aktiver</t>
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>34164</v>
+        <v>361576</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>119302</v>
+        <v>366067</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>139217</v>
+        <v>367218</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>72229</v>
+        <v>379817</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>85301</v>
+        <v>398268</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>36361</v>
+        <v>101</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>361576</v>
+        <v>101</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>366067</v>
+        <v>101</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>367218</v>
+        <v>101</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>379817</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n">
-        <v>51</v>
-      </c>
-      <c r="C25" s="16" t="n">
-        <v>101</v>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>101</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>101</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>101</v>
-      </c>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+          <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
       <c r="B26" s="16" t="n"/>
@@ -5327,7 +5284,7 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Reserve for udviklingsomkostninger</t>
+          <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
       <c r="B27" s="16" t="n"/>
@@ -5339,7 +5296,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
+          <t>Andre reserver</t>
         </is>
       </c>
       <c r="B28" s="16" t="n"/>
@@ -5351,63 +5308,63 @@
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>Andre reserver</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+          <t>Overført resultat</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="n">
+        <v>-10555</v>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>265202</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>289844</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>313053</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>316456</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>Overført resultat</t>
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>-9434</v>
+        <v>249495</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>-10555</v>
+        <v>265303</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>265202</v>
+        <v>289945</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>289844</v>
+        <v>313154</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>313053</v>
+        <v>316558</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>-9383</v>
-      </c>
-      <c r="C31" s="16" t="n">
-        <v>249495</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>265303</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>289945</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>313154</v>
-      </c>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
+          <t>Langfristede lån</t>
         </is>
       </c>
       <c r="B32" s="16" t="n"/>
@@ -5419,7 +5376,7 @@
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Langfristede lån</t>
+          <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
       <c r="B33" s="16" t="n"/>
@@ -5431,55 +5388,51 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
+          <t>Anden gæld (langfristet)</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>20456</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="D34" s="16" t="n"/>
       <c r="E34" s="16" t="n"/>
       <c r="F34" s="16" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (langfristet)</t>
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>13467</v>
+        <v>20456</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>20456</v>
-      </c>
-      <c r="D35" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="D35" s="16" t="n"/>
       <c r="E35" s="16" t="n"/>
       <c r="F35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>13467</v>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>20456</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
       <c r="E36" s="16" t="n"/>
       <c r="F36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B37" s="16" t="n"/>
@@ -5491,7 +5444,7 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B38" s="16" t="n"/>
@@ -5503,7 +5456,7 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B39" s="16" t="n"/>
@@ -5515,207 +5468,195 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="n">
+        <v>4206</v>
+      </c>
+      <c r="C40" s="16" t="n">
+        <v>3902</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>2745</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>2144</v>
+      </c>
+      <c r="F40" s="16" t="n">
+        <v>2689</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>659</v>
+        <v>39598</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>4206</v>
+        <v>21943</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>3902</v>
+        <v>40745</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>2745</v>
+        <v>35498</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>2144</v>
+        <v>45573</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n">
-        <v>12843</v>
-      </c>
-      <c r="C42" s="16" t="n">
-        <v>39598</v>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>21943</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>40745</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>35498</v>
-      </c>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B43" s="16" t="n"/>
       <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
+      <c r="D43" s="16" t="n">
+        <v>5072</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="F43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
       <c r="B44" s="16" t="n"/>
       <c r="C44" s="16" t="n"/>
       <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n">
-        <v>5072</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="n">
+        <v>36523</v>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>64479</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>21243</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>21443</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>22122</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
       <c r="B46" s="16" t="n">
-        <v>14480</v>
+        <v>11296</v>
       </c>
       <c r="C46" s="16" t="n">
-        <v>36523</v>
+        <v>10439</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>64479</v>
+        <v>7468</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>21243</v>
+        <v>7577</v>
       </c>
       <c r="F46" s="16" t="n">
-        <v>21443</v>
+        <v>11327</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B47" s="16" t="n">
-        <v>4296</v>
+        <v>91624</v>
       </c>
       <c r="C47" s="16" t="n">
-        <v>11296</v>
+        <v>100763</v>
       </c>
       <c r="D47" s="16" t="n">
-        <v>10439</v>
+        <v>77273</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>7468</v>
+        <v>66662</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>7577</v>
+        <v>81710</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>Kortfristede gældsforpligtelser</t>
+          <t>Gældsforpligtelser</t>
         </is>
       </c>
       <c r="B48" s="16" t="n">
-        <v>32278</v>
+        <v>112080</v>
       </c>
       <c r="C48" s="16" t="n">
-        <v>91624</v>
+        <v>100763</v>
       </c>
       <c r="D48" s="16" t="n">
-        <v>100763</v>
+        <v>77273</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>77273</v>
+        <v>66662</v>
       </c>
       <c r="F48" s="16" t="n">
-        <v>66662</v>
+        <v>81710</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>Gældsforpligtelser</t>
+          <t>Passiver</t>
         </is>
       </c>
       <c r="B49" s="16" t="n">
-        <v>45744</v>
+        <v>361576</v>
       </c>
       <c r="C49" s="16" t="n">
-        <v>112080</v>
+        <v>366067</v>
       </c>
       <c r="D49" s="16" t="n">
-        <v>100763</v>
+        <v>367218</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>77273</v>
+        <v>379817</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>66662</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>36361</v>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>361576</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>366067</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>367218</v>
-      </c>
-      <c r="F50" s="16" t="n">
-        <v>379817</v>
+        <v>398268</v>
       </c>
     </row>
   </sheetData>
@@ -5754,13 +5695,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6116,15 +6057,15 @@
         </is>
       </c>
       <c r="B20" s="24">
-        <f>'balance_raw_40333371'!$F$23</f>
+        <f>'balance_raw_40333371'!$F$22</f>
         <v/>
       </c>
       <c r="C20" s="24">
-        <f>'balance_raw_40333371'!$E$23</f>
+        <f>'balance_raw_40333371'!$E$22</f>
         <v/>
       </c>
       <c r="D20" s="24">
-        <f>'balance_raw_40333371'!$D$23</f>
+        <f>'balance_raw_40333371'!$D$22</f>
         <v/>
       </c>
       <c r="F20" s="25" t="inlineStr">
@@ -6171,15 +6112,15 @@
         </is>
       </c>
       <c r="B23" s="24">
-        <f>'balance_raw_40333371'!$F$31</f>
+        <f>'balance_raw_40333371'!$F$30</f>
         <v/>
       </c>
       <c r="C23" s="24">
-        <f>'balance_raw_40333371'!$E$31</f>
+        <f>'balance_raw_40333371'!$E$30</f>
         <v/>
       </c>
       <c r="D23" s="24">
-        <f>'balance_raw_40333371'!$D$31</f>
+        <f>'balance_raw_40333371'!$D$30</f>
         <v/>
       </c>
       <c r="F23" s="25" t="inlineStr">
@@ -6195,15 +6136,15 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>'balance_raw_40333371'!$F$50-'balance_raw_40333371'!$F$31</f>
+        <f>'balance_raw_40333371'!$F$49-'balance_raw_40333371'!$F$30</f>
         <v/>
       </c>
       <c r="C24" s="24">
-        <f>'balance_raw_40333371'!$E$50-'balance_raw_40333371'!$E$31</f>
+        <f>'balance_raw_40333371'!$E$49-'balance_raw_40333371'!$E$30</f>
         <v/>
       </c>
       <c r="D24" s="24">
-        <f>'balance_raw_40333371'!$D$50-'balance_raw_40333371'!$D$31</f>
+        <f>'balance_raw_40333371'!$D$49-'balance_raw_40333371'!$D$30</f>
         <v/>
       </c>
       <c r="F24" s="25" t="inlineStr">
@@ -6260,18 +6201,9 @@
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B28" s="24">
-        <f>'balance_raw_40333371'!$F$12</f>
-        <v/>
-      </c>
-      <c r="C28" s="24">
-        <f>'balance_raw_40333371'!$E$12</f>
-        <v/>
-      </c>
-      <c r="D28" s="24">
-        <f>'balance_raw_40333371'!$D$12</f>
-        <v/>
-      </c>
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
       <c r="F28" s="25" t="inlineStr">
         <is>
           <t>fsa:Inventories (eller fsa:ManufacturedGoodsAndGoodsForResale hvis total mangler).</t>
@@ -6285,15 +6217,15 @@
         </is>
       </c>
       <c r="B29" s="24">
-        <f>'balance_raw_40333371'!$F$13</f>
+        <f>'balance_raw_40333371'!$F$12</f>
         <v/>
       </c>
       <c r="C29" s="24">
-        <f>'balance_raw_40333371'!$E$13</f>
+        <f>'balance_raw_40333371'!$E$12</f>
         <v/>
       </c>
       <c r="D29" s="24">
-        <f>'balance_raw_40333371'!$D$13</f>
+        <f>'balance_raw_40333371'!$D$12</f>
         <v/>
       </c>
       <c r="F29" s="25" t="inlineStr">
@@ -6309,15 +6241,15 @@
         </is>
       </c>
       <c r="B30" s="24">
-        <f>'balance_raw_40333371'!$F$48</f>
+        <f>'balance_raw_40333371'!$F$47</f>
         <v/>
       </c>
       <c r="C30" s="24">
-        <f>'balance_raw_40333371'!$E$48</f>
+        <f>'balance_raw_40333371'!$E$47</f>
         <v/>
       </c>
       <c r="D30" s="24">
-        <f>'balance_raw_40333371'!$D$48</f>
+        <f>'balance_raw_40333371'!$D$47</f>
         <v/>
       </c>
       <c r="F30" s="25" t="inlineStr">
@@ -6474,7 +6406,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6592,7 +6524,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6768,7 +6700,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -6801,15 +6733,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_40333371'!$F$24="","—",IF(ABS(B21-'balance_raw_40333371'!$F$24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_40333371'!$F$24,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_40333371'!$F$23="","—",IF(ABS(B21-'balance_raw_40333371'!$F$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_40333371'!$F$23,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_40333371'!$E$24="","—",IF(ABS(C21-'balance_raw_40333371'!$E$24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_40333371'!$E$24,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_40333371'!$E$23="","—",IF(ABS(C21-'balance_raw_40333371'!$E$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_40333371'!$E$23,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_40333371'!$D$24="","—",IF(ABS(D21-'balance_raw_40333371'!$D$24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_40333371'!$D$24,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_40333371'!$D$23="","—",IF(ABS(D21-'balance_raw_40333371'!$D$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_40333371'!$D$23,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -6825,15 +6757,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw_40333371'!$F$50="","—",IF(ABS(B25-'balance_raw_40333371'!$F$50)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_40333371'!$F$50,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_40333371'!$F$49="","—",IF(ABS(B25-'balance_raw_40333371'!$F$49)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_40333371'!$F$49,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw_40333371'!$E$50="","—",IF(ABS(C25-'balance_raw_40333371'!$E$50)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_40333371'!$E$50,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_40333371'!$E$49="","—",IF(ABS(C25-'balance_raw_40333371'!$E$49)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_40333371'!$E$49,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw_40333371'!$D$50="","—",IF(ABS(D25-'balance_raw_40333371'!$D$50)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_40333371'!$D$50,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_40333371'!$D$49="","—",IF(ABS(D25-'balance_raw_40333371'!$D$49)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_40333371'!$D$49,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -6991,27 +6923,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7037,14 +6969,12 @@
         </is>
       </c>
       <c r="D3" s="35" t="n">
-        <v>815</v>
+        <v>3064</v>
       </c>
       <c r="E3" s="35" t="n">
-        <v>3064</v>
-      </c>
-      <c r="F3" s="35" t="n">
         <v>12902</v>
       </c>
+      <c r="F3" s="35" t="n"/>
       <c r="G3" s="35" t="n"/>
       <c r="H3" s="35" t="n"/>
       <c r="I3" s="36" t="inlineStr">
@@ -7097,14 +7027,12 @@
         </is>
       </c>
       <c r="D5" s="35" t="n">
+        <v>259949</v>
+      </c>
+      <c r="E5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="35" t="n">
-        <v>259949</v>
-      </c>
-      <c r="F5" s="35" t="n">
-        <v>0</v>
-      </c>
+      <c r="F5" s="35" t="n"/>
       <c r="G5" s="35" t="n"/>
       <c r="H5" s="35" t="n"/>
       <c r="I5" s="36" t="inlineStr">
